--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2BFC6-17BA-4437-8E39-69999B0F99E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B355EAF-FB5A-4225-B026-44FFD18A1FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,11 +807,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1119,9 +1120,63 @@
   <cols>
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="27.77734375" customWidth="1"/>
+    <col min="9" max="9" width="23.77734375" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" customWidth="1"/>
+    <col min="11" max="11" width="28.77734375" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
+    <col min="13" max="13" width="34.6640625" customWidth="1"/>
+    <col min="14" max="14" width="39.109375" customWidth="1"/>
+    <col min="15" max="15" width="30.44140625" customWidth="1"/>
+    <col min="16" max="16" width="34.88671875" customWidth="1"/>
+    <col min="17" max="17" width="76.5546875" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" customWidth="1"/>
+    <col min="20" max="20" width="20.77734375" customWidth="1"/>
+    <col min="21" max="21" width="28.33203125" customWidth="1"/>
+    <col min="22" max="22" width="32.33203125" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="24" width="26.33203125" customWidth="1"/>
+    <col min="25" max="25" width="29.33203125" customWidth="1"/>
+    <col min="26" max="26" width="36.6640625" customWidth="1"/>
+    <col min="27" max="27" width="28.5546875" customWidth="1"/>
+    <col min="28" max="28" width="43.44140625" customWidth="1"/>
+    <col min="29" max="29" width="28.6640625" customWidth="1"/>
+    <col min="30" max="30" width="26.109375" customWidth="1"/>
+    <col min="31" max="31" width="22.109375" customWidth="1"/>
+    <col min="32" max="32" width="22.77734375" customWidth="1"/>
+    <col min="33" max="33" width="21.44140625" customWidth="1"/>
+    <col min="34" max="34" width="22.44140625" customWidth="1"/>
+    <col min="35" max="35" width="20.44140625" customWidth="1"/>
+    <col min="36" max="36" width="21" customWidth="1"/>
+    <col min="37" max="37" width="20.77734375" customWidth="1"/>
+    <col min="38" max="38" width="18.77734375" customWidth="1"/>
+    <col min="39" max="39" width="19.33203125" customWidth="1"/>
+    <col min="40" max="40" width="32.5546875" customWidth="1"/>
+    <col min="41" max="41" width="27.33203125" customWidth="1"/>
+    <col min="42" max="42" width="26.109375" customWidth="1"/>
+    <col min="43" max="43" width="22.109375" customWidth="1"/>
+    <col min="44" max="44" width="19" customWidth="1"/>
+    <col min="45" max="45" width="24.44140625" customWidth="1"/>
+    <col min="46" max="46" width="23.33203125" customWidth="1"/>
+    <col min="47" max="47" width="23.21875" customWidth="1"/>
+    <col min="48" max="48" width="20.5546875" customWidth="1"/>
+    <col min="49" max="49" width="25.33203125" customWidth="1"/>
+    <col min="50" max="50" width="31.109375" customWidth="1"/>
+    <col min="51" max="51" width="30.21875" customWidth="1"/>
+    <col min="52" max="52" width="24.21875" customWidth="1"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1"/>
+    <col min="54" max="54" width="17.88671875" customWidth="1"/>
+    <col min="55" max="55" width="20.44140625" customWidth="1"/>
+    <col min="56" max="56" width="40" customWidth="1"/>
+    <col min="57" max="57" width="23.6640625" customWidth="1"/>
+    <col min="58" max="58" width="12.88671875" customWidth="1"/>
+    <col min="59" max="59" width="21.21875" customWidth="1"/>
+    <col min="60" max="60" width="16.44140625" customWidth="1"/>
+    <col min="61" max="61" width="24.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -67180,5 +67235,6 @@
   </sheetData>
   <autoFilter ref="G1:G364" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -46692,7 +46692,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>junior qulity assurance engineer</t>
+          <t>junior quality assurance engineer</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">

--- a/data/cleaned_data.xlsx
+++ b/data/cleaned_data.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AE2489-6252-44B9-9FC4-51F2BC0028CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A6BC83-53A1-4142-A450-9C07C47F613B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BJ$363</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="375">
   <si>
     <t>Type of Degree</t>
   </si>
@@ -355,9 +358,6 @@
     <t>Distinuish Achievement</t>
   </si>
   <si>
-    <t>production coordinator</t>
-  </si>
-  <si>
     <t>2016-07</t>
   </si>
   <si>
@@ -467,9 +467,6 @@
   </si>
   <si>
     <t>!st Place</t>
-  </si>
-  <si>
-    <t>electronics engineer</t>
   </si>
   <si>
     <t>3rd Place</t>
@@ -775,9 +772,6 @@
     <t>sales and administration</t>
   </si>
   <si>
-    <t>executive qa</t>
-  </si>
-  <si>
     <t>2021-09</t>
   </si>
   <si>
@@ -811,16 +805,10 @@
     <t>puchasing executive</t>
   </si>
   <si>
-    <t>operations analyst</t>
-  </si>
-  <si>
     <t>senior site reliability engineer</t>
   </si>
   <si>
     <t>management service officer</t>
-  </si>
-  <si>
-    <t>production exceative</t>
   </si>
   <si>
     <t>2022-12</t>
@@ -848,9 +836,6 @@
   </si>
   <si>
     <t>train controlling technical assistant</t>
-  </si>
-  <si>
-    <t>opertions analyst</t>
   </si>
   <si>
     <t>assistance electronic engineer</t>
@@ -889,13 +874,7 @@
     <t>associate data engineer</t>
   </si>
   <si>
-    <t>associate quality assouance engineer</t>
-  </si>
-  <si>
     <t>operation analyst</t>
-  </si>
-  <si>
-    <t>qa engineer</t>
   </si>
   <si>
     <t>2022-06</t>
@@ -917,9 +896,6 @@
   </si>
   <si>
     <t>system coordinator</t>
-  </si>
-  <si>
-    <t>engineering assistant</t>
   </si>
   <si>
     <t>2021-07</t>
@@ -952,16 +928,7 @@
     <t>technical executive</t>
   </si>
   <si>
-    <t>engineer executive</t>
-  </si>
-  <si>
     <t>associate operations analyst</t>
-  </si>
-  <si>
-    <t>executire bulk merchenclder</t>
-  </si>
-  <si>
-    <t>operations analysist</t>
   </si>
   <si>
     <t>junior it executive</t>
@@ -1034,9 +1001,6 @@
   </si>
   <si>
     <t>2023-04</t>
-  </si>
-  <si>
-    <t>intern business anylyst</t>
   </si>
   <si>
     <t>hr officer</t>
@@ -1153,9 +1117,6 @@
     <t>2017/2018, 2018/2019</t>
   </si>
   <si>
-    <t>software qa engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">2017/18,2018/2019                                                                       ASBIRES 2019                                                                                                                                                       1st runner up </t>
   </si>
   <si>
@@ -1175,6 +1136,18 @@
   </si>
   <si>
     <t xml:space="preserve">dean' s award list </t>
+  </si>
+  <si>
+    <t>executive quality assurance engineer</t>
+  </si>
+  <si>
+    <t>assistant electronic engineer</t>
+  </si>
+  <si>
+    <t>associate software quality assurance engineer</t>
+  </si>
+  <si>
+    <t>junior software quality assurance engineer</t>
   </si>
 </sst>
 </file>
@@ -1537,13 +1510,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BJ363"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
@@ -1792,7 +1766,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1980,7 +1954,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -2168,7 +2142,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -2353,7 +2327,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -2538,7 +2512,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -2723,7 +2697,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -2908,7 +2882,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -3090,7 +3064,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -3272,7 +3246,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -3457,7 +3431,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3642,7 +3616,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -3821,7 +3795,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -4003,7 +3977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -4188,7 +4162,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4376,7 +4350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -4564,7 +4538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -4746,7 +4720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -4928,7 +4902,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -5110,7 +5084,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -5289,7 +5263,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -5471,7 +5445,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>88</v>
       </c>
@@ -5653,7 +5627,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -5838,7 +5812,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -6023,7 +5997,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -6208,7 +6182,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -6390,7 +6364,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>88</v>
       </c>
@@ -6575,7 +6549,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -6760,7 +6734,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -6948,7 +6922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -6959,7 +6933,7 @@
         <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
         <v>73</v>
@@ -6968,7 +6942,7 @@
         <v>67</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H30">
         <v>52000</v>
@@ -7133,7 +7107,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -7144,7 +7118,7 @@
         <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>73</v>
@@ -7318,7 +7292,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -7500,13 +7474,13 @@
         <v>0</v>
       </c>
       <c r="BI32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BJ32" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -7517,7 +7491,7 @@
         <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>73</v>
@@ -7691,7 +7665,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>88</v>
       </c>
@@ -7702,7 +7676,7 @@
         <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
         <v>73</v>
@@ -7876,7 +7850,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -7887,7 +7861,7 @@
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
         <v>73</v>
@@ -7896,7 +7870,7 @@
         <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H35">
         <v>60000</v>
@@ -8061,7 +8035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -8072,7 +8046,7 @@
         <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
         <v>73</v>
@@ -8246,7 +8220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -8257,7 +8231,7 @@
         <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
         <v>73</v>
@@ -8428,13 +8402,13 @@
         <v>0</v>
       </c>
       <c r="BI37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BJ37" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -8445,7 +8419,7 @@
         <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38" t="s">
         <v>91</v>
@@ -8619,7 +8593,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -8630,7 +8604,7 @@
         <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39" t="s">
         <v>73</v>
@@ -8801,10 +8775,10 @@
         <v>0</v>
       </c>
       <c r="BJ39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -8815,7 +8789,7 @@
         <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
         <v>66</v>
@@ -8983,7 +8957,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -8994,7 +8968,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
         <v>73</v>
@@ -9003,7 +8977,7 @@
         <v>67</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H41">
         <v>80000</v>
@@ -9165,13 +9139,13 @@
         <v>0</v>
       </c>
       <c r="BI41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BJ41" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -9182,7 +9156,7 @@
         <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
         <v>91</v>
@@ -9191,7 +9165,7 @@
         <v>95</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H42">
         <v>20000</v>
@@ -9356,7 +9330,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>88</v>
       </c>
@@ -9538,7 +9512,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -9720,7 +9694,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -9902,7 +9876,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -9922,7 +9896,7 @@
         <v>100</v>
       </c>
       <c r="G46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H46">
         <v>30000</v>
@@ -10084,13 +10058,13 @@
         <v>0</v>
       </c>
       <c r="BI46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BJ46" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -10110,7 +10084,7 @@
         <v>100</v>
       </c>
       <c r="G47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H47">
         <v>32000</v>
@@ -10275,7 +10249,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -10457,7 +10431,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -10639,7 +10613,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -10821,7 +10795,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -10841,7 +10815,7 @@
         <v>100</v>
       </c>
       <c r="G51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H51">
         <v>39000</v>
@@ -11003,13 +10977,13 @@
         <v>0</v>
       </c>
       <c r="BI51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BJ51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -11029,7 +11003,7 @@
         <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H52">
         <v>43000</v>
@@ -11191,13 +11165,13 @@
         <v>1</v>
       </c>
       <c r="BI52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BJ52" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -11208,7 +11182,7 @@
         <v>76</v>
       </c>
       <c r="D53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E53" t="s">
         <v>73</v>
@@ -11382,7 +11356,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>88</v>
       </c>
@@ -11393,7 +11367,7 @@
         <v>97</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E54" t="s">
         <v>73</v>
@@ -11564,7 +11538,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -11575,7 +11549,7 @@
         <v>97</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E55" t="s">
         <v>73</v>
@@ -11743,13 +11717,13 @@
         <v>0</v>
       </c>
       <c r="BI55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BJ55" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>88</v>
       </c>
@@ -11928,7 +11902,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -11939,7 +11913,7 @@
         <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
         <v>91</v>
@@ -11948,7 +11922,7 @@
         <v>67</v>
       </c>
       <c r="G57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H57">
         <v>30000</v>
@@ -12113,7 +12087,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -12124,7 +12098,7 @@
         <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
         <v>91</v>
@@ -12133,7 +12107,7 @@
         <v>67</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H58">
         <v>40000</v>
@@ -12295,13 +12269,13 @@
         <v>0</v>
       </c>
       <c r="BI58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BJ58" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -12483,7 +12457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -12503,7 +12477,7 @@
         <v>67</v>
       </c>
       <c r="G60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H60">
         <v>15000</v>
@@ -12668,7 +12642,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -12679,7 +12653,7 @@
         <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61" t="s">
         <v>73</v>
@@ -12688,7 +12662,7 @@
         <v>67</v>
       </c>
       <c r="G61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H61">
         <v>40000</v>
@@ -12850,13 +12824,13 @@
         <v>1</v>
       </c>
       <c r="BI61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BJ61" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -12867,7 +12841,7 @@
         <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
         <v>73</v>
@@ -12876,7 +12850,7 @@
         <v>67</v>
       </c>
       <c r="G62" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H62">
         <v>35000</v>
@@ -13038,13 +13012,13 @@
         <v>1</v>
       </c>
       <c r="BI62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BJ62" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -13055,7 +13029,7 @@
         <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
         <v>73</v>
@@ -13226,7 +13200,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -13237,7 +13211,7 @@
         <v>64</v>
       </c>
       <c r="D64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E64" t="s">
         <v>73</v>
@@ -13408,7 +13382,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -13428,7 +13402,7 @@
         <v>67</v>
       </c>
       <c r="G65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H65">
         <v>40000</v>
@@ -13593,7 +13567,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -13769,13 +13743,13 @@
         <v>0</v>
       </c>
       <c r="BI66" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BJ66" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -13786,7 +13760,7 @@
         <v>76</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>73</v>
@@ -13954,13 +13928,13 @@
         <v>1</v>
       </c>
       <c r="BI67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BJ67" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -13971,7 +13945,7 @@
         <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="E68" t="s">
         <v>66</v>
@@ -13980,7 +13954,7 @@
         <v>67</v>
       </c>
       <c r="G68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -14139,13 +14113,13 @@
         <v>1</v>
       </c>
       <c r="BI68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="BJ68" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>62</v>
       </c>
@@ -14165,7 +14139,7 @@
         <v>100</v>
       </c>
       <c r="G69" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H69">
         <v>39000</v>
@@ -14330,7 +14304,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>62</v>
       </c>
@@ -14350,7 +14324,7 @@
         <v>67</v>
       </c>
       <c r="G70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H70">
         <v>50000</v>
@@ -14515,7 +14489,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>62</v>
       </c>
@@ -14526,7 +14500,7 @@
         <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
         <v>91</v>
@@ -14535,7 +14509,7 @@
         <v>67</v>
       </c>
       <c r="G71" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H71">
         <v>30000</v>
@@ -14700,7 +14674,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>88</v>
       </c>
@@ -14720,7 +14694,7 @@
         <v>95</v>
       </c>
       <c r="G72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H72">
         <v>39700</v>
@@ -14885,7 +14859,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -14896,7 +14870,7 @@
         <v>76</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
         <v>94</v>
@@ -14905,7 +14879,7 @@
         <v>67</v>
       </c>
       <c r="G73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H73">
         <v>20000</v>
@@ -15070,7 +15044,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -15081,7 +15055,7 @@
         <v>97</v>
       </c>
       <c r="D74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
         <v>73</v>
@@ -15090,7 +15064,7 @@
         <v>67</v>
       </c>
       <c r="G74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -15249,10 +15223,10 @@
         <v>0</v>
       </c>
       <c r="BJ74" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -15263,7 +15237,7 @@
         <v>97</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
         <v>91</v>
@@ -15272,7 +15246,7 @@
         <v>67</v>
       </c>
       <c r="G75" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -15431,10 +15405,10 @@
         <v>0</v>
       </c>
       <c r="BJ75" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>62</v>
       </c>
@@ -15454,7 +15428,7 @@
         <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H76">
         <v>39230</v>
@@ -15619,7 +15593,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -15630,7 +15604,7 @@
         <v>64</v>
       </c>
       <c r="D77" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E77" t="s">
         <v>73</v>
@@ -15639,7 +15613,7 @@
         <v>67</v>
       </c>
       <c r="G77" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H77">
         <v>50000</v>
@@ -15801,10 +15775,10 @@
         <v>1</v>
       </c>
       <c r="BJ77" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -15815,7 +15789,7 @@
         <v>64</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E78" t="s">
         <v>94</v>
@@ -15824,7 +15798,7 @@
         <v>67</v>
       </c>
       <c r="G78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H78">
         <v>32000</v>
@@ -15989,7 +15963,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>62</v>
       </c>
@@ -16000,7 +15974,7 @@
         <v>76</v>
       </c>
       <c r="D79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E79" t="s">
         <v>73</v>
@@ -16009,7 +15983,7 @@
         <v>67</v>
       </c>
       <c r="G79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H79">
         <v>50000</v>
@@ -16174,7 +16148,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>62</v>
       </c>
@@ -16185,7 +16159,7 @@
         <v>76</v>
       </c>
       <c r="D80" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E80" t="s">
         <v>73</v>
@@ -16194,7 +16168,7 @@
         <v>67</v>
       </c>
       <c r="G80" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H80">
         <v>30000</v>
@@ -16356,13 +16330,13 @@
         <v>0</v>
       </c>
       <c r="BI80" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BJ80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -16382,7 +16356,7 @@
         <v>100</v>
       </c>
       <c r="G81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H81">
         <v>37300</v>
@@ -16547,7 +16521,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>62</v>
       </c>
@@ -16567,7 +16541,7 @@
         <v>95</v>
       </c>
       <c r="G82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H82">
         <v>40000</v>
@@ -16729,13 +16703,13 @@
         <v>0</v>
       </c>
       <c r="BI82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="BJ82" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>62</v>
       </c>
@@ -16746,7 +16720,7 @@
         <v>64</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E83" t="s">
         <v>73</v>
@@ -16914,13 +16888,13 @@
         <v>0</v>
       </c>
       <c r="BI83" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="BJ83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>62</v>
       </c>
@@ -16931,7 +16905,7 @@
         <v>64</v>
       </c>
       <c r="D84" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E84" t="s">
         <v>73</v>
@@ -16940,7 +16914,7 @@
         <v>67</v>
       </c>
       <c r="G84" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H84">
         <v>55000</v>
@@ -17102,13 +17076,13 @@
         <v>0</v>
       </c>
       <c r="BI84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BJ84" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>62</v>
       </c>
@@ -17290,7 +17264,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>62</v>
       </c>
@@ -17301,7 +17275,7 @@
         <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E86" t="s">
         <v>73</v>
@@ -17310,7 +17284,7 @@
         <v>67</v>
       </c>
       <c r="G86" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H86">
         <v>42500</v>
@@ -17475,7 +17449,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>62</v>
       </c>
@@ -17486,7 +17460,7 @@
         <v>76</v>
       </c>
       <c r="D87" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E87" t="s">
         <v>73</v>
@@ -17495,7 +17469,7 @@
         <v>67</v>
       </c>
       <c r="G87" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H87">
         <v>45000</v>
@@ -17657,13 +17631,13 @@
         <v>0</v>
       </c>
       <c r="BI87" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="BJ87" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>62</v>
       </c>
@@ -17683,7 +17657,7 @@
         <v>67</v>
       </c>
       <c r="G88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -17845,7 +17819,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>62</v>
       </c>
@@ -18027,7 +18001,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>62</v>
       </c>
@@ -18209,7 +18183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>62</v>
       </c>
@@ -18220,7 +18194,7 @@
         <v>76</v>
       </c>
       <c r="D91" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E91" t="s">
         <v>73</v>
@@ -18229,7 +18203,7 @@
         <v>67</v>
       </c>
       <c r="G91" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H91">
         <v>22908</v>
@@ -18391,13 +18365,13 @@
         <v>0</v>
       </c>
       <c r="BI91" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="BJ91" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>62</v>
       </c>
@@ -18417,7 +18391,7 @@
         <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H92">
         <v>48000</v>
@@ -18582,7 +18556,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>62</v>
       </c>
@@ -18764,7 +18738,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -18775,7 +18749,7 @@
         <v>97</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E94" t="s">
         <v>66</v>
@@ -18943,13 +18917,13 @@
         <v>0</v>
       </c>
       <c r="BI94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="BJ94" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>62</v>
       </c>
@@ -18960,7 +18934,7 @@
         <v>97</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E95" t="s">
         <v>73</v>
@@ -18969,7 +18943,7 @@
         <v>67</v>
       </c>
       <c r="G95" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H95">
         <v>66000</v>
@@ -19134,7 +19108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>88</v>
       </c>
@@ -19145,7 +19119,7 @@
         <v>97</v>
       </c>
       <c r="D96" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E96" t="s">
         <v>91</v>
@@ -19313,10 +19287,10 @@
         <v>0</v>
       </c>
       <c r="BJ96" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="97" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>62</v>
       </c>
@@ -19327,7 +19301,7 @@
         <v>76</v>
       </c>
       <c r="D97" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E97" t="s">
         <v>91</v>
@@ -19336,7 +19310,7 @@
         <v>67</v>
       </c>
       <c r="G97" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -19498,7 +19472,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>62</v>
       </c>
@@ -19509,7 +19483,7 @@
         <v>76</v>
       </c>
       <c r="D98" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E98" t="s">
         <v>91</v>
@@ -19677,13 +19651,13 @@
         <v>1</v>
       </c>
       <c r="BI98" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="BJ98" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>88</v>
       </c>
@@ -19694,7 +19668,7 @@
         <v>97</v>
       </c>
       <c r="D99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E99" t="s">
         <v>66</v>
@@ -19703,7 +19677,7 @@
         <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -19862,13 +19836,13 @@
         <v>0</v>
       </c>
       <c r="BI99" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="BJ99" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="100" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>62</v>
       </c>
@@ -19879,7 +19853,7 @@
         <v>64</v>
       </c>
       <c r="D100" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E100" t="s">
         <v>73</v>
@@ -19888,7 +19862,7 @@
         <v>67</v>
       </c>
       <c r="G100" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H100">
         <v>50000</v>
@@ -20053,7 +20027,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>62</v>
       </c>
@@ -20064,7 +20038,7 @@
         <v>76</v>
       </c>
       <c r="D101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E101" t="s">
         <v>73</v>
@@ -20073,7 +20047,7 @@
         <v>95</v>
       </c>
       <c r="G101" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H101">
         <v>28800</v>
@@ -20235,13 +20209,13 @@
         <v>1</v>
       </c>
       <c r="BI101" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="BJ101" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>62</v>
       </c>
@@ -20261,7 +20235,7 @@
         <v>67</v>
       </c>
       <c r="G102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H102">
         <v>25000</v>
@@ -20426,7 +20400,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>62</v>
       </c>
@@ -20437,7 +20411,7 @@
         <v>76</v>
       </c>
       <c r="D103" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E103" t="s">
         <v>91</v>
@@ -20446,7 +20420,7 @@
         <v>67</v>
       </c>
       <c r="G103" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H103">
         <v>40000</v>
@@ -20611,7 +20585,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>62</v>
       </c>
@@ -20622,7 +20596,7 @@
         <v>76</v>
       </c>
       <c r="D104" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
         <v>73</v>
@@ -20631,7 +20605,7 @@
         <v>67</v>
       </c>
       <c r="G104" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H104">
         <v>45000</v>
@@ -20793,10 +20767,10 @@
         <v>0</v>
       </c>
       <c r="BJ104" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="105" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>62</v>
       </c>
@@ -20807,7 +20781,7 @@
         <v>76</v>
       </c>
       <c r="D105" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E105" t="s">
         <v>73</v>
@@ -20816,7 +20790,7 @@
         <v>67</v>
       </c>
       <c r="G105" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H105">
         <v>26000</v>
@@ -20978,13 +20952,13 @@
         <v>0</v>
       </c>
       <c r="BI105" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="BJ105" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>62</v>
       </c>
@@ -20995,7 +20969,7 @@
         <v>76</v>
       </c>
       <c r="D106" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E106" t="s">
         <v>73</v>
@@ -21004,7 +20978,7 @@
         <v>67</v>
       </c>
       <c r="G106" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H106">
         <v>55000</v>
@@ -21169,7 +21143,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>62</v>
       </c>
@@ -21180,7 +21154,7 @@
         <v>76</v>
       </c>
       <c r="D107" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E107" t="s">
         <v>94</v>
@@ -21189,7 +21163,7 @@
         <v>67</v>
       </c>
       <c r="G107" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H107">
         <v>47000</v>
@@ -21351,13 +21325,13 @@
         <v>0</v>
       </c>
       <c r="BI107" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BJ107" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>62</v>
       </c>
@@ -21368,7 +21342,7 @@
         <v>76</v>
       </c>
       <c r="D108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E108" t="s">
         <v>73</v>
@@ -21377,7 +21351,7 @@
         <v>95</v>
       </c>
       <c r="G108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H108">
         <v>28800</v>
@@ -21542,7 +21516,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="109" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>62</v>
       </c>
@@ -21553,7 +21527,7 @@
         <v>76</v>
       </c>
       <c r="D109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E109" t="s">
         <v>73</v>
@@ -21562,7 +21536,7 @@
         <v>95</v>
       </c>
       <c r="G109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H109">
         <v>37000</v>
@@ -21727,7 +21701,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="110" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>88</v>
       </c>
@@ -21747,7 +21721,7 @@
         <v>95</v>
       </c>
       <c r="G110" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H110">
         <v>44810</v>
@@ -21912,7 +21886,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="111" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>62</v>
       </c>
@@ -21923,7 +21897,7 @@
         <v>76</v>
       </c>
       <c r="D111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E111" t="s">
         <v>73</v>
@@ -21932,7 +21906,7 @@
         <v>67</v>
       </c>
       <c r="G111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -22091,13 +22065,13 @@
         <v>0</v>
       </c>
       <c r="BI111" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BJ111" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>62</v>
       </c>
@@ -22108,7 +22082,7 @@
         <v>76</v>
       </c>
       <c r="D112" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
         <v>73</v>
@@ -22117,7 +22091,7 @@
         <v>67</v>
       </c>
       <c r="G112" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H112">
         <v>36000</v>
@@ -22279,13 +22253,13 @@
         <v>0</v>
       </c>
       <c r="BI112" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BJ112" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>62</v>
       </c>
@@ -22305,7 +22279,7 @@
         <v>95</v>
       </c>
       <c r="G113" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H113">
         <v>37010</v>
@@ -22470,7 +22444,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="114" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>62</v>
       </c>
@@ -22490,7 +22464,7 @@
         <v>95</v>
       </c>
       <c r="G114" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H114">
         <v>37010</v>
@@ -22652,13 +22626,13 @@
         <v>0</v>
       </c>
       <c r="BI114" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BJ114" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="115" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>62</v>
       </c>
@@ -22840,7 +22814,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="116" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>88</v>
       </c>
@@ -22860,7 +22834,7 @@
         <v>100</v>
       </c>
       <c r="G116" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H116">
         <v>40000</v>
@@ -23022,13 +22996,13 @@
         <v>1</v>
       </c>
       <c r="BI116" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="BJ116" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="117" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>62</v>
       </c>
@@ -23048,7 +23022,7 @@
         <v>100</v>
       </c>
       <c r="G117" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H117">
         <v>40000</v>
@@ -23210,13 +23184,13 @@
         <v>1</v>
       </c>
       <c r="BI117" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="BJ117" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="118" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -23236,7 +23210,7 @@
         <v>100</v>
       </c>
       <c r="G118" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H118">
         <v>40300</v>
@@ -23398,13 +23372,13 @@
         <v>1</v>
       </c>
       <c r="BI118" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BJ118" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="119" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>62</v>
       </c>
@@ -23424,7 +23398,7 @@
         <v>100</v>
       </c>
       <c r="G119" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H119">
         <v>45000</v>
@@ -23589,7 +23563,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="120" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>88</v>
       </c>
@@ -23609,7 +23583,7 @@
         <v>100</v>
       </c>
       <c r="G120" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H120">
         <v>40304</v>
@@ -23774,7 +23748,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="121" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>88</v>
       </c>
@@ -23794,7 +23768,7 @@
         <v>100</v>
       </c>
       <c r="G121" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H121">
         <v>40300</v>
@@ -23959,7 +23933,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="122" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>62</v>
       </c>
@@ -23979,7 +23953,7 @@
         <v>100</v>
       </c>
       <c r="G122" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H122">
         <v>45000</v>
@@ -24141,13 +24115,13 @@
         <v>0</v>
       </c>
       <c r="BI122" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BJ122" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="123" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>62</v>
       </c>
@@ -24167,7 +24141,7 @@
         <v>95</v>
       </c>
       <c r="G123" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H123">
         <v>40000</v>
@@ -24332,7 +24306,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="124" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -24343,7 +24317,7 @@
         <v>64</v>
       </c>
       <c r="D124" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E124" t="s">
         <v>73</v>
@@ -24352,7 +24326,7 @@
         <v>95</v>
       </c>
       <c r="G124" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H124">
         <v>37000</v>
@@ -24517,7 +24491,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="125" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>62</v>
       </c>
@@ -24528,7 +24502,7 @@
         <v>64</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E125" t="s">
         <v>73</v>
@@ -24699,7 +24673,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>62</v>
       </c>
@@ -24719,7 +24693,7 @@
         <v>67</v>
       </c>
       <c r="G126" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H126">
         <v>30000</v>
@@ -24884,7 +24858,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="127" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>88</v>
       </c>
@@ -25063,7 +25037,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>88</v>
       </c>
@@ -25242,7 +25216,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>88</v>
       </c>
@@ -25253,7 +25227,7 @@
         <v>97</v>
       </c>
       <c r="D129" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E129" t="s">
         <v>73</v>
@@ -25262,7 +25236,7 @@
         <v>95</v>
       </c>
       <c r="G129" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -25424,7 +25398,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>62</v>
       </c>
@@ -25435,7 +25409,7 @@
         <v>76</v>
       </c>
       <c r="D130" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E130" t="s">
         <v>73</v>
@@ -25444,7 +25418,7 @@
         <v>95</v>
       </c>
       <c r="G130" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H130">
         <v>37000</v>
@@ -25609,7 +25583,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="131" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>62</v>
       </c>
@@ -25620,7 +25594,7 @@
         <v>76</v>
       </c>
       <c r="D131" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E131" t="s">
         <v>73</v>
@@ -25629,7 +25603,7 @@
         <v>95</v>
       </c>
       <c r="G131" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H131">
         <v>37000</v>
@@ -25791,13 +25765,13 @@
         <v>0</v>
       </c>
       <c r="BI131" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BJ131" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="132" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>62</v>
       </c>
@@ -25979,7 +25953,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>62</v>
       </c>
@@ -25999,7 +25973,7 @@
         <v>67</v>
       </c>
       <c r="G133" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H133">
         <v>100000</v>
@@ -26164,7 +26138,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>88</v>
       </c>
@@ -26343,7 +26317,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>88</v>
       </c>
@@ -26363,7 +26337,7 @@
         <v>67</v>
       </c>
       <c r="G135" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -26525,7 +26499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>62</v>
       </c>
@@ -26704,13 +26678,13 @@
         <v>1</v>
       </c>
       <c r="BI136" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BJ136" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>62</v>
       </c>
@@ -26721,7 +26695,7 @@
         <v>76</v>
       </c>
       <c r="D137" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E137" t="s">
         <v>73</v>
@@ -26889,10 +26863,10 @@
         <v>0</v>
       </c>
       <c r="BJ137" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="138" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>62</v>
       </c>
@@ -27074,7 +27048,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="139" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>88</v>
       </c>
@@ -27253,13 +27227,13 @@
         <v>0</v>
       </c>
       <c r="BI139" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BJ139" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="140" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>62</v>
       </c>
@@ -27270,7 +27244,7 @@
         <v>76</v>
       </c>
       <c r="D140" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E140" t="s">
         <v>66</v>
@@ -27438,13 +27412,13 @@
         <v>0</v>
       </c>
       <c r="BI140" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="BJ140" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="141" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>62</v>
       </c>
@@ -27455,7 +27429,7 @@
         <v>76</v>
       </c>
       <c r="D141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E141" t="s">
         <v>66</v>
@@ -27623,13 +27597,13 @@
         <v>0</v>
       </c>
       <c r="BI141" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="BJ141" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>62</v>
       </c>
@@ -27640,7 +27614,7 @@
         <v>64</v>
       </c>
       <c r="D142" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E142" t="s">
         <v>73</v>
@@ -27649,7 +27623,7 @@
         <v>67</v>
       </c>
       <c r="G142" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H142">
         <v>30000</v>
@@ -27814,7 +27788,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="143" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>62</v>
       </c>
@@ -27825,7 +27799,7 @@
         <v>64</v>
       </c>
       <c r="D143" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E143" t="s">
         <v>73</v>
@@ -27834,7 +27808,7 @@
         <v>67</v>
       </c>
       <c r="G143" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H143">
         <v>65000</v>
@@ -27999,7 +27973,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="144" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>88</v>
       </c>
@@ -28010,7 +27984,7 @@
         <v>97</v>
       </c>
       <c r="D144" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E144" t="s">
         <v>66</v>
@@ -28178,13 +28152,13 @@
         <v>0</v>
       </c>
       <c r="BI144" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BJ144" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="145" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>62</v>
       </c>
@@ -28366,7 +28340,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="146" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>62</v>
       </c>
@@ -28386,7 +28360,7 @@
         <v>67</v>
       </c>
       <c r="G146" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H146">
         <v>40000</v>
@@ -28551,7 +28525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>62</v>
       </c>
@@ -28733,7 +28707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>62</v>
       </c>
@@ -28744,7 +28718,7 @@
         <v>64</v>
       </c>
       <c r="D148" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E148" t="s">
         <v>73</v>
@@ -28753,7 +28727,7 @@
         <v>67</v>
       </c>
       <c r="G148" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H148">
         <v>25000</v>
@@ -28918,7 +28892,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="149" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>62</v>
       </c>
@@ -28929,7 +28903,7 @@
         <v>76</v>
       </c>
       <c r="D149" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E149" t="s">
         <v>73</v>
@@ -28938,7 +28912,7 @@
         <v>67</v>
       </c>
       <c r="G149" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H149">
         <v>45000</v>
@@ -29114,7 +29088,7 @@
         <v>64</v>
       </c>
       <c r="D150" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E150" t="s">
         <v>73</v>
@@ -29123,7 +29097,7 @@
         <v>67</v>
       </c>
       <c r="G150" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H150">
         <v>40000</v>
@@ -29288,7 +29262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>62</v>
       </c>
@@ -29470,7 +29444,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="152" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>62</v>
       </c>
@@ -29652,7 +29626,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="153" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>62</v>
       </c>
@@ -29834,7 +29808,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="154" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -29845,7 +29819,7 @@
         <v>76</v>
       </c>
       <c r="D154" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E154" t="s">
         <v>73</v>
@@ -29854,7 +29828,7 @@
         <v>67</v>
       </c>
       <c r="G154" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H154">
         <v>35000</v>
@@ -30016,10 +29990,10 @@
         <v>0</v>
       </c>
       <c r="BJ154" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -30030,7 +30004,7 @@
         <v>64</v>
       </c>
       <c r="D155" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E155" t="s">
         <v>66</v>
@@ -30039,7 +30013,7 @@
         <v>67</v>
       </c>
       <c r="G155" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H155">
         <v>50000</v>
@@ -30204,7 +30178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>88</v>
       </c>
@@ -30383,13 +30357,13 @@
         <v>0</v>
       </c>
       <c r="BI156" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BJ156" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="157" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -30400,7 +30374,7 @@
         <v>76</v>
       </c>
       <c r="D157" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E157" t="s">
         <v>73</v>
@@ -30409,7 +30383,7 @@
         <v>95</v>
       </c>
       <c r="G157" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H157">
         <v>23672</v>
@@ -30571,13 +30545,13 @@
         <v>0</v>
       </c>
       <c r="BI157" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BJ157" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>88</v>
       </c>
@@ -30756,7 +30730,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="159" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -30776,7 +30750,7 @@
         <v>95</v>
       </c>
       <c r="G159" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H159">
         <v>43823</v>
@@ -30941,7 +30915,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="160" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>62</v>
       </c>
@@ -30952,7 +30926,7 @@
         <v>76</v>
       </c>
       <c r="D160" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E160" t="s">
         <v>73</v>
@@ -30961,7 +30935,7 @@
         <v>67</v>
       </c>
       <c r="G160" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H160">
         <v>22500</v>
@@ -31126,7 +31100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>62</v>
       </c>
@@ -31146,7 +31120,7 @@
         <v>100</v>
       </c>
       <c r="G161" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H161">
         <v>42823</v>
@@ -31311,7 +31285,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="162" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>88</v>
       </c>
@@ -31322,7 +31296,7 @@
         <v>97</v>
       </c>
       <c r="D162" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E162" t="s">
         <v>73</v>
@@ -31331,7 +31305,7 @@
         <v>67</v>
       </c>
       <c r="G162" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H162">
         <v>150000</v>
@@ -31493,10 +31467,10 @@
         <v>0</v>
       </c>
       <c r="BJ162" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="163" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>88</v>
       </c>
@@ -31678,7 +31652,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="164" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>62</v>
       </c>
@@ -31698,7 +31672,7 @@
         <v>100</v>
       </c>
       <c r="G164" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H164">
         <v>43000</v>
@@ -31863,7 +31837,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="165" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>62</v>
       </c>
@@ -31883,7 +31857,7 @@
         <v>95</v>
       </c>
       <c r="G165" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H165">
         <v>43000</v>
@@ -32048,7 +32022,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="166" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>88</v>
       </c>
@@ -32068,7 +32042,7 @@
         <v>95</v>
       </c>
       <c r="G166" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H166">
         <v>43800</v>
@@ -32233,7 +32207,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="167" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>62</v>
       </c>
@@ -32244,7 +32218,7 @@
         <v>97</v>
       </c>
       <c r="D167" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E167" t="s">
         <v>73</v>
@@ -32253,7 +32227,7 @@
         <v>67</v>
       </c>
       <c r="G167" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H167">
         <v>50000</v>
@@ -32418,7 +32392,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>88</v>
       </c>
@@ -32438,7 +32412,7 @@
         <v>95</v>
       </c>
       <c r="G168" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H168">
         <v>44000</v>
@@ -32603,7 +32577,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="169" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>62</v>
       </c>
@@ -32614,7 +32588,7 @@
         <v>97</v>
       </c>
       <c r="D169" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E169" t="s">
         <v>73</v>
@@ -32623,7 +32597,7 @@
         <v>67</v>
       </c>
       <c r="G169" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H169">
         <v>60000</v>
@@ -32785,10 +32759,10 @@
         <v>0</v>
       </c>
       <c r="BJ169" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="170" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>62</v>
       </c>
@@ -32808,7 +32782,7 @@
         <v>67</v>
       </c>
       <c r="G170" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H170">
         <v>80000</v>
@@ -32973,7 +32947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>62</v>
       </c>
@@ -32993,7 +32967,7 @@
         <v>95</v>
       </c>
       <c r="G171" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H171">
         <v>43000</v>
@@ -33158,7 +33132,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="172" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>62</v>
       </c>
@@ -33169,7 +33143,7 @@
         <v>64</v>
       </c>
       <c r="D172" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E172" t="s">
         <v>73</v>
@@ -33178,7 +33152,7 @@
         <v>67</v>
       </c>
       <c r="G172" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H172">
         <v>57000</v>
@@ -33343,7 +33317,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>62</v>
       </c>
@@ -33354,7 +33328,7 @@
         <v>76</v>
       </c>
       <c r="D173" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E173" t="s">
         <v>73</v>
@@ -33363,7 +33337,7 @@
         <v>67</v>
       </c>
       <c r="G173" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H173">
         <v>50000</v>
@@ -33528,7 +33502,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="174" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>62</v>
       </c>
@@ -33548,7 +33522,7 @@
         <v>100</v>
       </c>
       <c r="G174" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H174">
         <v>48000</v>
@@ -33713,7 +33687,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="175" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>62</v>
       </c>
@@ -33724,7 +33698,7 @@
         <v>76</v>
       </c>
       <c r="D175" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E175" t="s">
         <v>73</v>
@@ -33733,7 +33707,7 @@
         <v>67</v>
       </c>
       <c r="G175" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H175">
         <v>55000</v>
@@ -33898,7 +33872,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="176" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>62</v>
       </c>
@@ -33909,7 +33883,7 @@
         <v>64</v>
       </c>
       <c r="D176" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E176" t="s">
         <v>66</v>
@@ -33918,7 +33892,7 @@
         <v>100</v>
       </c>
       <c r="G176" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H176">
         <v>200000</v>
@@ -34080,10 +34054,10 @@
         <v>0</v>
       </c>
       <c r="BJ176" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="177" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -34103,7 +34077,7 @@
         <v>67</v>
       </c>
       <c r="G177" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -34276,7 +34250,7 @@
         <v>64</v>
       </c>
       <c r="D178" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E178" t="s">
         <v>73</v>
@@ -34285,7 +34259,7 @@
         <v>67</v>
       </c>
       <c r="G178" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H178">
         <v>55000</v>
@@ -34450,7 +34424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>88</v>
       </c>
@@ -34461,7 +34435,7 @@
         <v>97</v>
       </c>
       <c r="D179" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E179" t="s">
         <v>73</v>
@@ -34470,7 +34444,7 @@
         <v>67</v>
       </c>
       <c r="G179" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -34629,10 +34603,10 @@
         <v>1</v>
       </c>
       <c r="BJ179" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="180" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>62</v>
       </c>
@@ -34652,7 +34626,7 @@
         <v>95</v>
       </c>
       <c r="G180" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H180">
         <v>43000</v>
@@ -34828,7 +34802,7 @@
         <v>64</v>
       </c>
       <c r="D181" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E181" t="s">
         <v>73</v>
@@ -34837,7 +34811,7 @@
         <v>67</v>
       </c>
       <c r="G181" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H181">
         <v>60000</v>
@@ -35002,7 +34976,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="182" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>62</v>
       </c>
@@ -35022,7 +34996,7 @@
         <v>95</v>
       </c>
       <c r="G182" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H182">
         <v>40000</v>
@@ -35187,7 +35161,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="183" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -35207,7 +35181,7 @@
         <v>67</v>
       </c>
       <c r="G183" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H183">
         <v>65000</v>
@@ -35372,7 +35346,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="184" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>62</v>
       </c>
@@ -35383,7 +35357,7 @@
         <v>76</v>
       </c>
       <c r="D184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E184" t="s">
         <v>73</v>
@@ -35392,7 +35366,7 @@
         <v>67</v>
       </c>
       <c r="G184" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H184">
         <v>75000</v>
@@ -35557,7 +35531,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="185" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -35568,7 +35542,7 @@
         <v>76</v>
       </c>
       <c r="D185" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E185" t="s">
         <v>73</v>
@@ -35577,7 +35551,7 @@
         <v>67</v>
       </c>
       <c r="G185" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H185">
         <v>45000</v>
@@ -35742,7 +35716,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>62</v>
       </c>
@@ -35762,7 +35736,7 @@
         <v>67</v>
       </c>
       <c r="G186" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H186">
         <v>120000</v>
@@ -35927,7 +35901,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>62</v>
       </c>
@@ -35938,7 +35912,7 @@
         <v>64</v>
       </c>
       <c r="D187" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E187" t="s">
         <v>73</v>
@@ -35947,7 +35921,7 @@
         <v>67</v>
       </c>
       <c r="G187" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H187">
         <v>40000</v>
@@ -36109,10 +36083,10 @@
         <v>0</v>
       </c>
       <c r="BJ187" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="188" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>62</v>
       </c>
@@ -36123,7 +36097,7 @@
         <v>76</v>
       </c>
       <c r="D188" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E188" t="s">
         <v>66</v>
@@ -36132,7 +36106,7 @@
         <v>67</v>
       </c>
       <c r="G188" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H188">
         <v>22000</v>
@@ -36297,7 +36271,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="189" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>62</v>
       </c>
@@ -36308,7 +36282,7 @@
         <v>76</v>
       </c>
       <c r="D189" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E189" t="s">
         <v>73</v>
@@ -36317,7 +36291,7 @@
         <v>67</v>
       </c>
       <c r="G189" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H189">
         <v>65000</v>
@@ -36479,7 +36453,7 @@
         <v>0</v>
       </c>
       <c r="BJ189" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="190" spans="1:62" x14ac:dyDescent="0.3">
@@ -36493,7 +36467,7 @@
         <v>76</v>
       </c>
       <c r="D190" t="s">
-        <v>251</v>
+        <v>371</v>
       </c>
       <c r="E190" t="s">
         <v>73</v>
@@ -36502,7 +36476,7 @@
         <v>67</v>
       </c>
       <c r="G190" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H190">
         <v>96500</v>
@@ -36667,7 +36641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>62</v>
       </c>
@@ -36687,7 +36661,7 @@
         <v>67</v>
       </c>
       <c r="G191" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H191">
         <v>30000</v>
@@ -36852,7 +36826,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="192" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>62</v>
       </c>
@@ -36863,7 +36837,7 @@
         <v>76</v>
       </c>
       <c r="D192" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E192" t="s">
         <v>73</v>
@@ -36872,7 +36846,7 @@
         <v>67</v>
       </c>
       <c r="G192" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H192">
         <v>50000</v>
@@ -37037,7 +37011,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="193" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>62</v>
       </c>
@@ -37057,7 +37031,7 @@
         <v>95</v>
       </c>
       <c r="G193" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H193">
         <v>43000</v>
@@ -37222,7 +37196,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>88</v>
       </c>
@@ -37242,7 +37216,7 @@
         <v>95</v>
       </c>
       <c r="G194" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H194">
         <v>43800</v>
@@ -37407,7 +37381,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="195" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>88</v>
       </c>
@@ -37427,7 +37401,7 @@
         <v>100</v>
       </c>
       <c r="G195" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H195">
         <v>43200</v>
@@ -37592,7 +37566,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="196" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>62</v>
       </c>
@@ -37603,7 +37577,7 @@
         <v>76</v>
       </c>
       <c r="D196" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E196" t="s">
         <v>73</v>
@@ -37612,7 +37586,7 @@
         <v>67</v>
       </c>
       <c r="G196" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I196">
         <v>0</v>
@@ -37774,7 +37748,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="197" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>88</v>
       </c>
@@ -37785,7 +37759,7 @@
         <v>97</v>
       </c>
       <c r="D197" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E197" t="s">
         <v>73</v>
@@ -37794,7 +37768,7 @@
         <v>67</v>
       </c>
       <c r="G197" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H197">
         <v>75000</v>
@@ -37959,7 +37933,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="198" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>88</v>
       </c>
@@ -37970,7 +37944,7 @@
         <v>97</v>
       </c>
       <c r="D198" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E198" t="s">
         <v>73</v>
@@ -37979,7 +37953,7 @@
         <v>67</v>
       </c>
       <c r="G198" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H198">
         <v>50000</v>
@@ -38144,7 +38118,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="199" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>62</v>
       </c>
@@ -38155,7 +38129,7 @@
         <v>76</v>
       </c>
       <c r="D199" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E199" t="s">
         <v>73</v>
@@ -38164,7 +38138,7 @@
         <v>67</v>
       </c>
       <c r="G199" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -38326,7 +38300,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="200" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>88</v>
       </c>
@@ -38337,7 +38311,7 @@
         <v>64</v>
       </c>
       <c r="D200" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E200" t="s">
         <v>66</v>
@@ -38502,10 +38476,10 @@
         <v>0</v>
       </c>
       <c r="BJ200" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="201" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>62</v>
       </c>
@@ -38516,7 +38490,7 @@
         <v>64</v>
       </c>
       <c r="D201" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E201" t="s">
         <v>73</v>
@@ -38525,7 +38499,7 @@
         <v>67</v>
       </c>
       <c r="G201" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I201">
         <v>0</v>
@@ -38687,7 +38661,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>62</v>
       </c>
@@ -38698,7 +38672,7 @@
         <v>76</v>
       </c>
       <c r="D202" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E202" t="s">
         <v>73</v>
@@ -38866,7 +38840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="203" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>62</v>
       </c>
@@ -38886,7 +38860,7 @@
         <v>100</v>
       </c>
       <c r="G203" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H203">
         <v>42000</v>
@@ -39051,7 +39025,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="204" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>62</v>
       </c>
@@ -39062,7 +39036,7 @@
         <v>76</v>
       </c>
       <c r="D204" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E204" t="s">
         <v>73</v>
@@ -39071,7 +39045,7 @@
         <v>67</v>
       </c>
       <c r="G204" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H204">
         <v>80000</v>
@@ -39233,10 +39207,10 @@
         <v>0</v>
       </c>
       <c r="BJ204" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="205" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>62</v>
       </c>
@@ -39247,7 +39221,7 @@
         <v>76</v>
       </c>
       <c r="D205" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E205" t="s">
         <v>73</v>
@@ -39256,7 +39230,7 @@
         <v>67</v>
       </c>
       <c r="G205" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H205">
         <v>77000</v>
@@ -39421,7 +39395,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="206" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>62</v>
       </c>
@@ -39441,7 +39415,7 @@
         <v>67</v>
       </c>
       <c r="G206" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H206">
         <v>20000</v>
@@ -39606,7 +39580,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="207" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>62</v>
       </c>
@@ -39617,7 +39591,7 @@
         <v>64</v>
       </c>
       <c r="D207" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E207" t="s">
         <v>73</v>
@@ -39626,7 +39600,7 @@
         <v>67</v>
       </c>
       <c r="G207" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H207">
         <v>40000</v>
@@ -39791,7 +39765,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="208" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>62</v>
       </c>
@@ -39811,7 +39785,7 @@
         <v>67</v>
       </c>
       <c r="G208" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H208">
         <v>60000</v>
@@ -39976,7 +39950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="209" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>62</v>
       </c>
@@ -39987,7 +39961,7 @@
         <v>64</v>
       </c>
       <c r="D209" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="E209" t="s">
         <v>73</v>
@@ -39996,7 +39970,7 @@
         <v>67</v>
       </c>
       <c r="G209" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H209">
         <v>50000</v>
@@ -40161,7 +40135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="210" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>62</v>
       </c>
@@ -40172,7 +40146,7 @@
         <v>76</v>
       </c>
       <c r="D210" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E210" t="s">
         <v>73</v>
@@ -40181,7 +40155,7 @@
         <v>67</v>
       </c>
       <c r="G210" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I210">
         <v>0</v>
@@ -40343,7 +40317,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="211" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>62</v>
       </c>
@@ -40354,7 +40328,7 @@
         <v>76</v>
       </c>
       <c r="D211" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E211" t="s">
         <v>73</v>
@@ -40363,7 +40337,7 @@
         <v>95</v>
       </c>
       <c r="G211" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H211">
         <v>52000</v>
@@ -40528,7 +40502,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="212" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>62</v>
       </c>
@@ -40539,7 +40513,7 @@
         <v>76</v>
       </c>
       <c r="D212" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E212" t="s">
         <v>94</v>
@@ -40710,7 +40684,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="213" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>62</v>
       </c>
@@ -40721,7 +40695,7 @@
         <v>76</v>
       </c>
       <c r="D213" t="s">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c r="E213" t="s">
         <v>73</v>
@@ -40730,7 +40704,7 @@
         <v>67</v>
       </c>
       <c r="G213" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H213">
         <v>120000</v>
@@ -40895,7 +40869,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="214" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>62</v>
       </c>
@@ -40906,7 +40880,7 @@
         <v>76</v>
       </c>
       <c r="D214" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E214" t="s">
         <v>73</v>
@@ -41074,10 +41048,10 @@
         <v>0</v>
       </c>
       <c r="BJ214" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="215" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>62</v>
       </c>
@@ -41097,7 +41071,7 @@
         <v>67</v>
       </c>
       <c r="G215" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H215">
         <v>100000</v>
@@ -41262,7 +41236,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="216" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -41273,7 +41247,7 @@
         <v>76</v>
       </c>
       <c r="D216" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E216" t="s">
         <v>66</v>
@@ -41438,10 +41412,10 @@
         <v>0</v>
       </c>
       <c r="BJ216" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="217" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>62</v>
       </c>
@@ -41452,7 +41426,7 @@
         <v>76</v>
       </c>
       <c r="D217" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E217" t="s">
         <v>73</v>
@@ -41461,7 +41435,7 @@
         <v>67</v>
       </c>
       <c r="G217" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -41623,7 +41597,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="218" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>62</v>
       </c>
@@ -41634,7 +41608,7 @@
         <v>76</v>
       </c>
       <c r="D218" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E218" t="s">
         <v>73</v>
@@ -41643,7 +41617,7 @@
         <v>67</v>
       </c>
       <c r="G218" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H218">
         <v>701000</v>
@@ -41808,7 +41782,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="219" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>62</v>
       </c>
@@ -41819,7 +41793,7 @@
         <v>76</v>
       </c>
       <c r="D219" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E219" t="s">
         <v>73</v>
@@ -41828,7 +41802,7 @@
         <v>67</v>
       </c>
       <c r="G219" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H219">
         <v>50000</v>
@@ -41990,10 +41964,10 @@
         <v>0</v>
       </c>
       <c r="BJ219" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="220" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>62</v>
       </c>
@@ -42004,7 +41978,7 @@
         <v>97</v>
       </c>
       <c r="D220" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E220" t="s">
         <v>73</v>
@@ -42013,7 +41987,7 @@
         <v>67</v>
       </c>
       <c r="G220" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H220">
         <v>65000</v>
@@ -42178,7 +42152,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>62</v>
       </c>
@@ -42189,7 +42163,7 @@
         <v>97</v>
       </c>
       <c r="D221" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E221" t="s">
         <v>73</v>
@@ -42198,7 +42172,7 @@
         <v>67</v>
       </c>
       <c r="G221" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H221">
         <v>100000</v>
@@ -42363,7 +42337,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="222" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>88</v>
       </c>
@@ -42374,7 +42348,7 @@
         <v>97</v>
       </c>
       <c r="D222" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E222" t="s">
         <v>73</v>
@@ -42383,7 +42357,7 @@
         <v>67</v>
       </c>
       <c r="G222" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H222">
         <v>100000</v>
@@ -42545,10 +42519,10 @@
         <v>1</v>
       </c>
       <c r="BJ222" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="223" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>62</v>
       </c>
@@ -42559,7 +42533,7 @@
         <v>64</v>
       </c>
       <c r="D223" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E223" t="s">
         <v>91</v>
@@ -42568,7 +42542,7 @@
         <v>67</v>
       </c>
       <c r="G223" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I223">
         <v>0</v>
@@ -42730,7 +42704,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="224" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>88</v>
       </c>
@@ -42750,7 +42724,7 @@
         <v>100</v>
       </c>
       <c r="G224" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H224">
         <v>48823</v>
@@ -42915,7 +42889,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="225" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>62</v>
       </c>
@@ -42926,7 +42900,7 @@
         <v>76</v>
       </c>
       <c r="D225" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E225" t="s">
         <v>66</v>
@@ -42935,7 +42909,7 @@
         <v>67</v>
       </c>
       <c r="G225" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H225">
         <v>65000</v>
@@ -43100,7 +43074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="226" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>62</v>
       </c>
@@ -43111,7 +43085,7 @@
         <v>76</v>
       </c>
       <c r="D226" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E226" t="s">
         <v>73</v>
@@ -43120,7 +43094,7 @@
         <v>67</v>
       </c>
       <c r="G226" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H226">
         <v>30000</v>
@@ -43285,7 +43259,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="227" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>62</v>
       </c>
@@ -43296,7 +43270,7 @@
         <v>76</v>
       </c>
       <c r="D227" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E227" t="s">
         <v>73</v>
@@ -43305,7 +43279,7 @@
         <v>67</v>
       </c>
       <c r="G227" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H227">
         <v>40000</v>
@@ -43470,7 +43444,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="228" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>62</v>
       </c>
@@ -43490,7 +43464,7 @@
         <v>95</v>
       </c>
       <c r="G228" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H228">
         <v>43000</v>
@@ -43655,7 +43629,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="229" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>88</v>
       </c>
@@ -43845,7 +43819,7 @@
         <v>64</v>
       </c>
       <c r="D230" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E230" t="s">
         <v>73</v>
@@ -43854,7 +43828,7 @@
         <v>67</v>
       </c>
       <c r="G230" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H230">
         <v>60000</v>
@@ -44019,7 +43993,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="231" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>88</v>
       </c>
@@ -44039,7 +44013,7 @@
         <v>95</v>
       </c>
       <c r="G231" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H231">
         <v>48000</v>
@@ -44204,7 +44178,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="232" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>88</v>
       </c>
@@ -44215,7 +44189,7 @@
         <v>107</v>
       </c>
       <c r="D232" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E232" t="s">
         <v>91</v>
@@ -44224,7 +44198,7 @@
         <v>67</v>
       </c>
       <c r="G232" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H232">
         <v>50000</v>
@@ -44389,7 +44363,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="233" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>62</v>
       </c>
@@ -44400,7 +44374,7 @@
         <v>64</v>
       </c>
       <c r="D233" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E233" t="s">
         <v>73</v>
@@ -44571,7 +44545,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="234" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>62</v>
       </c>
@@ -44582,7 +44556,7 @@
         <v>97</v>
       </c>
       <c r="D234" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E234" t="s">
         <v>66</v>
@@ -44591,7 +44565,7 @@
         <v>67</v>
       </c>
       <c r="G234" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H234">
         <v>65000</v>
@@ -44756,7 +44730,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="235" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>62</v>
       </c>
@@ -44767,7 +44741,7 @@
         <v>64</v>
       </c>
       <c r="D235" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E235" t="s">
         <v>73</v>
@@ -44776,7 +44750,7 @@
         <v>67</v>
       </c>
       <c r="G235" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H235">
         <v>50000</v>
@@ -44941,7 +44915,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="236" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>62</v>
       </c>
@@ -44952,7 +44926,7 @@
         <v>76</v>
       </c>
       <c r="D236" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E236" t="s">
         <v>66</v>
@@ -44961,7 +44935,7 @@
         <v>67</v>
       </c>
       <c r="G236" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H236">
         <v>55000</v>
@@ -45126,7 +45100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="237" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>88</v>
       </c>
@@ -45137,7 +45111,7 @@
         <v>64</v>
       </c>
       <c r="D237" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E237" t="s">
         <v>73</v>
@@ -45146,7 +45120,7 @@
         <v>67</v>
       </c>
       <c r="G237" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H237">
         <v>50000</v>
@@ -45311,7 +45285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="238" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>62</v>
       </c>
@@ -45322,7 +45296,7 @@
         <v>97</v>
       </c>
       <c r="D238" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E238" t="s">
         <v>73</v>
@@ -45331,7 +45305,7 @@
         <v>67</v>
       </c>
       <c r="G238" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I238">
         <v>0</v>
@@ -45490,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="BJ238" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="239" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>88</v>
       </c>
@@ -45513,7 +45487,7 @@
         <v>67</v>
       </c>
       <c r="G239" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H239">
         <v>85000</v>
@@ -45689,7 +45663,7 @@
         <v>64</v>
       </c>
       <c r="D240" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="E240" t="s">
         <v>73</v>
@@ -45860,7 +45834,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="241" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>62</v>
       </c>
@@ -45871,7 +45845,7 @@
         <v>97</v>
       </c>
       <c r="D241" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E241" t="s">
         <v>73</v>
@@ -46042,7 +46016,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>62</v>
       </c>
@@ -46062,7 +46036,7 @@
         <v>67</v>
       </c>
       <c r="G242" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H242">
         <v>40000</v>
@@ -46238,7 +46212,7 @@
         <v>64</v>
       </c>
       <c r="D243" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="E243" t="s">
         <v>73</v>
@@ -46247,7 +46221,7 @@
         <v>67</v>
       </c>
       <c r="G243" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H243">
         <v>90000</v>
@@ -46412,7 +46386,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="244" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>62</v>
       </c>
@@ -46432,7 +46406,7 @@
         <v>67</v>
       </c>
       <c r="G244" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I244">
         <v>0</v>
@@ -46594,7 +46568,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="245" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>62</v>
       </c>
@@ -46605,7 +46579,7 @@
         <v>76</v>
       </c>
       <c r="D245" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E245" t="s">
         <v>73</v>
@@ -46614,7 +46588,7 @@
         <v>67</v>
       </c>
       <c r="G245" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H245">
         <v>80000</v>
@@ -46779,7 +46753,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="246" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>88</v>
       </c>
@@ -46799,7 +46773,7 @@
         <v>67</v>
       </c>
       <c r="G246" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H246">
         <v>100000</v>
@@ -46964,7 +46938,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="247" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>62</v>
       </c>
@@ -46975,7 +46949,7 @@
         <v>64</v>
       </c>
       <c r="D247" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E247" t="s">
         <v>73</v>
@@ -46984,7 +46958,7 @@
         <v>67</v>
       </c>
       <c r="G247" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H247">
         <v>55000</v>
@@ -47146,10 +47120,10 @@
         <v>1</v>
       </c>
       <c r="BJ247" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="248" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>88</v>
       </c>
@@ -47169,7 +47143,7 @@
         <v>67</v>
       </c>
       <c r="G248" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H248">
         <v>150000</v>
@@ -47334,7 +47308,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="249" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>88</v>
       </c>
@@ -47345,7 +47319,7 @@
         <v>107</v>
       </c>
       <c r="D249" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E249" t="s">
         <v>73</v>
@@ -47354,7 +47328,7 @@
         <v>67</v>
       </c>
       <c r="G249" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H249">
         <v>110000</v>
@@ -47519,7 +47493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="250" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>62</v>
       </c>
@@ -47539,7 +47513,7 @@
         <v>100</v>
       </c>
       <c r="G250" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H250">
         <v>50000</v>
@@ -47704,7 +47678,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="251" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>62</v>
       </c>
@@ -47715,7 +47689,7 @@
         <v>64</v>
       </c>
       <c r="D251" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E251" t="s">
         <v>73</v>
@@ -47724,7 +47698,7 @@
         <v>67</v>
       </c>
       <c r="G251" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I251">
         <v>0</v>
@@ -47886,7 +47860,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="252" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>88</v>
       </c>
@@ -47906,7 +47880,7 @@
         <v>95</v>
       </c>
       <c r="G252" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H252">
         <v>48800</v>
@@ -48071,7 +48045,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>62</v>
       </c>
@@ -48091,7 +48065,7 @@
         <v>67</v>
       </c>
       <c r="G253" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H253">
         <v>60000</v>
@@ -48256,7 +48230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="254" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>62</v>
       </c>
@@ -48267,7 +48241,7 @@
         <v>76</v>
       </c>
       <c r="D254" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E254" t="s">
         <v>73</v>
@@ -48276,7 +48250,7 @@
         <v>67</v>
       </c>
       <c r="G254" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H254">
         <v>90000</v>
@@ -48441,7 +48415,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="255" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>88</v>
       </c>
@@ -48452,7 +48426,7 @@
         <v>97</v>
       </c>
       <c r="D255" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E255" t="s">
         <v>73</v>
@@ -48461,7 +48435,7 @@
         <v>67</v>
       </c>
       <c r="G255" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H255">
         <v>70000</v>
@@ -48626,7 +48600,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="256" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>62</v>
       </c>
@@ -48637,7 +48611,7 @@
         <v>97</v>
       </c>
       <c r="D256" t="s">
-        <v>299</v>
+        <v>372</v>
       </c>
       <c r="E256" t="s">
         <v>73</v>
@@ -48646,7 +48620,7 @@
         <v>67</v>
       </c>
       <c r="G256" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H256">
         <v>69000</v>
@@ -48811,7 +48785,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="257" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>88</v>
       </c>
@@ -48822,7 +48796,7 @@
         <v>97</v>
       </c>
       <c r="D257" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E257" t="s">
         <v>73</v>
@@ -48831,7 +48805,7 @@
         <v>67</v>
       </c>
       <c r="G257" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H257">
         <v>45000</v>
@@ -48993,10 +48967,10 @@
         <v>0</v>
       </c>
       <c r="BJ257" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="258" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>88</v>
       </c>
@@ -49007,7 +48981,7 @@
         <v>107</v>
       </c>
       <c r="D258" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E258" t="s">
         <v>73</v>
@@ -49016,7 +48990,7 @@
         <v>67</v>
       </c>
       <c r="G258" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="H258">
         <v>173000</v>
@@ -49181,7 +49155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="259" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>88</v>
       </c>
@@ -49192,7 +49166,7 @@
         <v>97</v>
       </c>
       <c r="D259" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E259" t="s">
         <v>73</v>
@@ -49201,7 +49175,7 @@
         <v>67</v>
       </c>
       <c r="G259" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H259">
         <v>50000</v>
@@ -49366,7 +49340,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="260" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>62</v>
       </c>
@@ -49377,7 +49351,7 @@
         <v>76</v>
       </c>
       <c r="D260" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="E260" t="s">
         <v>73</v>
@@ -49545,10 +49519,10 @@
         <v>0</v>
       </c>
       <c r="BJ260" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="261" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -49559,7 +49533,7 @@
         <v>64</v>
       </c>
       <c r="D261" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E261" t="s">
         <v>73</v>
@@ -49568,7 +49542,7 @@
         <v>67</v>
       </c>
       <c r="G261" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -49730,7 +49704,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="262" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>62</v>
       </c>
@@ -49750,7 +49724,7 @@
         <v>67</v>
       </c>
       <c r="G262" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -49912,7 +49886,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="263" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>62</v>
       </c>
@@ -49932,7 +49906,7 @@
         <v>67</v>
       </c>
       <c r="G263" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -50094,7 +50068,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="264" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>62</v>
       </c>
@@ -50105,7 +50079,7 @@
         <v>97</v>
       </c>
       <c r="D264" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E264" t="s">
         <v>73</v>
@@ -50114,7 +50088,7 @@
         <v>67</v>
       </c>
       <c r="G264" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H264">
         <v>50000</v>
@@ -50279,7 +50253,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="265" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>62</v>
       </c>
@@ -50290,7 +50264,7 @@
         <v>76</v>
       </c>
       <c r="D265" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E265" t="s">
         <v>91</v>
@@ -50299,7 +50273,7 @@
         <v>67</v>
       </c>
       <c r="G265" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H265">
         <v>60000</v>
@@ -50464,7 +50438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="266" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>62</v>
       </c>
@@ -50475,7 +50449,7 @@
         <v>76</v>
       </c>
       <c r="D266" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E266" t="s">
         <v>73</v>
@@ -50646,7 +50620,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="267" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>62</v>
       </c>
@@ -50666,7 +50640,7 @@
         <v>67</v>
       </c>
       <c r="G267" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H267">
         <v>120000</v>
@@ -50831,7 +50805,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="268" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>62</v>
       </c>
@@ -50842,7 +50816,7 @@
         <v>97</v>
       </c>
       <c r="D268" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E268" t="s">
         <v>73</v>
@@ -50851,7 +50825,7 @@
         <v>67</v>
       </c>
       <c r="G268" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H268">
         <v>50000</v>
@@ -51013,10 +50987,10 @@
         <v>0</v>
       </c>
       <c r="BJ268" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>88</v>
       </c>
@@ -51027,7 +51001,7 @@
         <v>107</v>
       </c>
       <c r="D269" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E269" t="s">
         <v>73</v>
@@ -51036,7 +51010,7 @@
         <v>67</v>
       </c>
       <c r="G269" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H269">
         <v>60000</v>
@@ -51201,7 +51175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="270" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>62</v>
       </c>
@@ -51212,7 +51186,7 @@
         <v>76</v>
       </c>
       <c r="D270" t="s">
-        <v>310</v>
+        <v>86</v>
       </c>
       <c r="E270" t="s">
         <v>91</v>
@@ -51221,7 +51195,7 @@
         <v>67</v>
       </c>
       <c r="G270" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H270">
         <v>50000</v>
@@ -51386,7 +51360,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="271" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>62</v>
       </c>
@@ -51406,7 +51380,7 @@
         <v>67</v>
       </c>
       <c r="G271" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -51571,7 +51545,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="272" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>62</v>
       </c>
@@ -51591,7 +51565,7 @@
         <v>95</v>
       </c>
       <c r="G272" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I272">
         <v>0</v>
@@ -51753,7 +51727,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="273" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>88</v>
       </c>
@@ -51764,7 +51738,7 @@
         <v>97</v>
       </c>
       <c r="D273" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E273" t="s">
         <v>73</v>
@@ -51773,7 +51747,7 @@
         <v>67</v>
       </c>
       <c r="G273" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H273">
         <v>55000</v>
@@ -51938,7 +51912,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="274" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>62</v>
       </c>
@@ -51949,7 +51923,7 @@
         <v>64</v>
       </c>
       <c r="D274" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E274" t="s">
         <v>73</v>
@@ -51958,7 +51932,7 @@
         <v>67</v>
       </c>
       <c r="G274" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H274">
         <v>25000</v>
@@ -52123,7 +52097,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="275" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>88</v>
       </c>
@@ -52134,7 +52108,7 @@
         <v>97</v>
       </c>
       <c r="D275" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E275" t="s">
         <v>66</v>
@@ -52143,7 +52117,7 @@
         <v>95</v>
       </c>
       <c r="G275" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H275">
         <v>105250</v>
@@ -52308,7 +52282,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="276" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>62</v>
       </c>
@@ -52319,7 +52293,7 @@
         <v>76</v>
       </c>
       <c r="D276" t="s">
-        <v>312</v>
+        <v>220</v>
       </c>
       <c r="E276" t="s">
         <v>73</v>
@@ -52484,10 +52458,10 @@
         <v>1</v>
       </c>
       <c r="BJ276" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="277" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>62</v>
       </c>
@@ -52507,7 +52481,7 @@
         <v>95</v>
       </c>
       <c r="G277" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H277">
         <v>48000</v>
@@ -52672,7 +52646,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="278" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>88</v>
       </c>
@@ -52854,7 +52828,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="279" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>62</v>
       </c>
@@ -52865,7 +52839,7 @@
         <v>76</v>
       </c>
       <c r="D279" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="E279" t="s">
         <v>73</v>
@@ -53036,7 +53010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="280" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>62</v>
       </c>
@@ -53047,7 +53021,7 @@
         <v>64</v>
       </c>
       <c r="D280" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E280" t="s">
         <v>73</v>
@@ -53218,7 +53192,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="281" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>88</v>
       </c>
@@ -53238,7 +53212,7 @@
         <v>95</v>
       </c>
       <c r="G281" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H281">
         <v>48800</v>
@@ -53403,7 +53377,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="282" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>88</v>
       </c>
@@ -53423,7 +53397,7 @@
         <v>95</v>
       </c>
       <c r="G282" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H282">
         <v>48800</v>
@@ -53588,7 +53562,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="283" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>62</v>
       </c>
@@ -53608,7 +53582,7 @@
         <v>95</v>
       </c>
       <c r="G283" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H283">
         <v>48000</v>
@@ -53773,7 +53747,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="284" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>88</v>
       </c>
@@ -53793,7 +53767,7 @@
         <v>100</v>
       </c>
       <c r="G284" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H284">
         <v>48823</v>
@@ -53958,7 +53932,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="285" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>62</v>
       </c>
@@ -53969,7 +53943,7 @@
         <v>64</v>
       </c>
       <c r="D285" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E285" t="s">
         <v>73</v>
@@ -53978,7 +53952,7 @@
         <v>67</v>
       </c>
       <c r="G285" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H285">
         <v>49300</v>
@@ -54143,7 +54117,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="286" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>62</v>
       </c>
@@ -54154,7 +54128,7 @@
         <v>64</v>
       </c>
       <c r="D286" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="E286" t="s">
         <v>91</v>
@@ -54163,7 +54137,7 @@
         <v>67</v>
       </c>
       <c r="G286" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="H286">
         <v>25000</v>
@@ -54328,7 +54302,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="287" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>62</v>
       </c>
@@ -54339,7 +54313,7 @@
         <v>64</v>
       </c>
       <c r="D287" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E287" t="s">
         <v>66</v>
@@ -54348,7 +54322,7 @@
         <v>67</v>
       </c>
       <c r="G287" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H287">
         <v>100000</v>
@@ -54513,7 +54487,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="288" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>62</v>
       </c>
@@ -54524,7 +54498,7 @@
         <v>64</v>
       </c>
       <c r="D288" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="E288" t="s">
         <v>73</v>
@@ -54533,7 +54507,7 @@
         <v>67</v>
       </c>
       <c r="G288" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="H288">
         <v>55000</v>
@@ -54695,10 +54669,10 @@
         <v>0</v>
       </c>
       <c r="BJ288" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="289" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>62</v>
       </c>
@@ -54709,7 +54683,7 @@
         <v>64</v>
       </c>
       <c r="D289" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E289" t="s">
         <v>73</v>
@@ -54718,7 +54692,7 @@
         <v>67</v>
       </c>
       <c r="G289" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H289">
         <v>85000</v>
@@ -54883,7 +54857,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="290" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>88</v>
       </c>
@@ -54903,7 +54877,7 @@
         <v>95</v>
       </c>
       <c r="G290" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="H290">
         <v>48875</v>
@@ -55068,7 +55042,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="291" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>62</v>
       </c>
@@ -55088,7 +55062,7 @@
         <v>95</v>
       </c>
       <c r="G291" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="H291">
         <v>45000</v>
@@ -55253,7 +55227,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="292" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>62</v>
       </c>
@@ -55264,7 +55238,7 @@
         <v>97</v>
       </c>
       <c r="D292" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E292" t="s">
         <v>66</v>
@@ -55432,13 +55406,13 @@
         <v>1</v>
       </c>
       <c r="BI292" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="BJ292" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="293" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>88</v>
       </c>
@@ -55449,7 +55423,7 @@
         <v>64</v>
       </c>
       <c r="D293" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E293" t="s">
         <v>73</v>
@@ -55458,7 +55432,7 @@
         <v>95</v>
       </c>
       <c r="G293" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H293">
         <v>75000</v>
@@ -55620,13 +55594,13 @@
         <v>0</v>
       </c>
       <c r="BI293" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="BJ293" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="294" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>62</v>
       </c>
@@ -55637,7 +55611,7 @@
         <v>64</v>
       </c>
       <c r="D294" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="E294" t="s">
         <v>66</v>
@@ -55646,7 +55620,7 @@
         <v>67</v>
       </c>
       <c r="G294" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H294">
         <v>60000</v>
@@ -55811,7 +55785,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="295" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>62</v>
       </c>
@@ -55822,7 +55796,7 @@
         <v>64</v>
       </c>
       <c r="D295" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E295" t="s">
         <v>73</v>
@@ -55831,7 +55805,7 @@
         <v>67</v>
       </c>
       <c r="G295" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="I295">
         <v>0</v>
@@ -55990,10 +55964,10 @@
         <v>0</v>
       </c>
       <c r="BJ295" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="296" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>62</v>
       </c>
@@ -56004,7 +55978,7 @@
         <v>64</v>
       </c>
       <c r="D296" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E296" t="s">
         <v>94</v>
@@ -56013,7 +55987,7 @@
         <v>67</v>
       </c>
       <c r="G296" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="I296">
         <v>0</v>
@@ -56172,13 +56146,13 @@
         <v>0</v>
       </c>
       <c r="BI296" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="BJ296" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="297" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>62</v>
       </c>
@@ -56189,7 +56163,7 @@
         <v>64</v>
       </c>
       <c r="D297" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E297" t="s">
         <v>73</v>
@@ -56198,7 +56172,7 @@
         <v>67</v>
       </c>
       <c r="G297" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="I297">
         <v>0</v>
@@ -56357,13 +56331,13 @@
         <v>0</v>
       </c>
       <c r="BI297" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="BJ297" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="298" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>62</v>
       </c>
@@ -56374,7 +56348,7 @@
         <v>64</v>
       </c>
       <c r="D298" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E298" t="s">
         <v>91</v>
@@ -56383,7 +56357,7 @@
         <v>67</v>
       </c>
       <c r="G298" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H298">
         <v>20000</v>
@@ -56548,7 +56522,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="299" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>62</v>
       </c>
@@ -56559,7 +56533,7 @@
         <v>64</v>
       </c>
       <c r="D299" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E299" t="s">
         <v>91</v>
@@ -56568,7 +56542,7 @@
         <v>67</v>
       </c>
       <c r="G299" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I299">
         <v>0</v>
@@ -56727,7 +56701,7 @@
         <v>0</v>
       </c>
       <c r="BI299" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="BJ299" t="s">
         <v>82</v>
@@ -56744,7 +56718,7 @@
         <v>64</v>
       </c>
       <c r="D300" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E300" t="s">
         <v>73</v>
@@ -56753,7 +56727,7 @@
         <v>67</v>
       </c>
       <c r="G300" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H300">
         <v>50000</v>
@@ -56918,7 +56892,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="301" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>62</v>
       </c>
@@ -56929,7 +56903,7 @@
         <v>64</v>
       </c>
       <c r="D301" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="E301" t="s">
         <v>73</v>
@@ -56938,7 +56912,7 @@
         <v>67</v>
       </c>
       <c r="G301" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H301">
         <v>27000</v>
@@ -57103,7 +57077,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="302" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>88</v>
       </c>
@@ -57114,7 +57088,7 @@
         <v>97</v>
       </c>
       <c r="D302" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E302" t="s">
         <v>73</v>
@@ -57123,7 +57097,7 @@
         <v>67</v>
       </c>
       <c r="G302" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H302">
         <v>70000</v>
@@ -57288,7 +57262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="303" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>62</v>
       </c>
@@ -57299,7 +57273,7 @@
         <v>64</v>
       </c>
       <c r="D303" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E303" t="s">
         <v>91</v>
@@ -57308,7 +57282,7 @@
         <v>100</v>
       </c>
       <c r="G303" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H303">
         <v>20000</v>
@@ -57473,7 +57447,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="304" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>62</v>
       </c>
@@ -57484,7 +57458,7 @@
         <v>97</v>
       </c>
       <c r="D304" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E304" t="s">
         <v>73</v>
@@ -57493,7 +57467,7 @@
         <v>67</v>
       </c>
       <c r="G304" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H304">
         <v>25000</v>
@@ -57658,7 +57632,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="305" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>62</v>
       </c>
@@ -57669,7 +57643,7 @@
         <v>64</v>
       </c>
       <c r="D305" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="E305" t="s">
         <v>91</v>
@@ -57678,7 +57652,7 @@
         <v>67</v>
       </c>
       <c r="G305" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H305">
         <v>35000</v>
@@ -57854,7 +57828,7 @@
         <v>97</v>
       </c>
       <c r="D306" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E306" t="s">
         <v>73</v>
@@ -57863,7 +57837,7 @@
         <v>67</v>
       </c>
       <c r="G306" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H306">
         <v>42000</v>
@@ -58028,7 +58002,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="307" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>62</v>
       </c>
@@ -58039,7 +58013,7 @@
         <v>97</v>
       </c>
       <c r="D307" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="E307" t="s">
         <v>73</v>
@@ -58048,7 +58022,7 @@
         <v>67</v>
       </c>
       <c r="G307" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H307">
         <v>35000</v>
@@ -58210,13 +58184,13 @@
         <v>0</v>
       </c>
       <c r="BI307" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="BJ307" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="308" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>88</v>
       </c>
@@ -58236,7 +58210,7 @@
         <v>67</v>
       </c>
       <c r="G308" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="I308">
         <v>0</v>
@@ -58398,7 +58372,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="309" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>88</v>
       </c>
@@ -58418,7 +58392,7 @@
         <v>95</v>
       </c>
       <c r="G309" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H309">
         <v>48000</v>
@@ -58583,7 +58557,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="310" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>88</v>
       </c>
@@ -58603,7 +58577,7 @@
         <v>95</v>
       </c>
       <c r="G310" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H310">
         <v>40920</v>
@@ -58768,7 +58742,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="311" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>62</v>
       </c>
@@ -58779,7 +58753,7 @@
         <v>64</v>
       </c>
       <c r="D311" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E311" t="s">
         <v>73</v>
@@ -58788,7 +58762,7 @@
         <v>67</v>
       </c>
       <c r="G311" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H311">
         <v>150000</v>
@@ -58950,10 +58924,10 @@
         <v>0</v>
       </c>
       <c r="BJ311" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="312" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>62</v>
       </c>
@@ -58964,7 +58938,7 @@
         <v>64</v>
       </c>
       <c r="D312" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="E312" t="s">
         <v>66</v>
@@ -59129,10 +59103,10 @@
         <v>0</v>
       </c>
       <c r="BJ312" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="313" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>62</v>
       </c>
@@ -59143,7 +59117,7 @@
         <v>64</v>
       </c>
       <c r="D313" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="E313" t="s">
         <v>73</v>
@@ -59152,7 +59126,7 @@
         <v>67</v>
       </c>
       <c r="G313" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H313">
         <v>65000</v>
@@ -59314,10 +59288,10 @@
         <v>0</v>
       </c>
       <c r="BJ313" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="314" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>62</v>
       </c>
@@ -59328,7 +59302,7 @@
         <v>64</v>
       </c>
       <c r="D314" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E314" t="s">
         <v>91</v>
@@ -59499,7 +59473,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="315" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>62</v>
       </c>
@@ -59510,7 +59484,7 @@
         <v>97</v>
       </c>
       <c r="D315" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="E315" t="s">
         <v>73</v>
@@ -59519,7 +59493,7 @@
         <v>67</v>
       </c>
       <c r="G315" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H315">
         <v>85000</v>
@@ -59684,7 +59658,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="316" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>88</v>
       </c>
@@ -59695,7 +59669,7 @@
         <v>97</v>
       </c>
       <c r="D316" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="E316" t="s">
         <v>73</v>
@@ -59866,7 +59840,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="317" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>88</v>
       </c>
@@ -59877,7 +59851,7 @@
         <v>97</v>
       </c>
       <c r="D317" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="E317" t="s">
         <v>73</v>
@@ -59886,7 +59860,7 @@
         <v>67</v>
       </c>
       <c r="G317" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="I317">
         <v>0</v>
@@ -60045,13 +60019,13 @@
         <v>0</v>
       </c>
       <c r="BI317" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BJ317" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="318" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>62</v>
       </c>
@@ -60071,7 +60045,7 @@
         <v>67</v>
       </c>
       <c r="G318" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="H318">
         <v>50000</v>
@@ -60236,7 +60210,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="319" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>88</v>
       </c>
@@ -60247,7 +60221,7 @@
         <v>97</v>
       </c>
       <c r="D319" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E319" t="s">
         <v>73</v>
@@ -60256,7 +60230,7 @@
         <v>67</v>
       </c>
       <c r="G319" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I319">
         <v>0</v>
@@ -60415,13 +60389,13 @@
         <v>0</v>
       </c>
       <c r="BI319" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="BJ319" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="320" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>62</v>
       </c>
@@ -60432,7 +60406,7 @@
         <v>64</v>
       </c>
       <c r="D320" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E320" t="s">
         <v>73</v>
@@ -60600,10 +60574,10 @@
         <v>0</v>
       </c>
       <c r="BJ320" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="321" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>62</v>
       </c>
@@ -60614,7 +60588,7 @@
         <v>64</v>
       </c>
       <c r="D321" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E321" t="s">
         <v>73</v>
@@ -60796,7 +60770,7 @@
         <v>97</v>
       </c>
       <c r="D322" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E322" t="s">
         <v>66</v>
@@ -60964,13 +60938,13 @@
         <v>1</v>
       </c>
       <c r="BI322" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="BJ322" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="323" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>62</v>
       </c>
@@ -60981,7 +60955,7 @@
         <v>64</v>
       </c>
       <c r="D323" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="E323" t="s">
         <v>73</v>
@@ -60990,7 +60964,7 @@
         <v>67</v>
       </c>
       <c r="G323" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H323">
         <v>40000</v>
@@ -61152,10 +61126,10 @@
         <v>0</v>
       </c>
       <c r="BJ323" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="324" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>62</v>
       </c>
@@ -61166,7 +61140,7 @@
         <v>64</v>
       </c>
       <c r="D324" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="E324" t="s">
         <v>66</v>
@@ -61175,7 +61149,7 @@
         <v>67</v>
       </c>
       <c r="G324" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H324">
         <v>88000</v>
@@ -61340,7 +61314,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="325" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>88</v>
       </c>
@@ -61351,7 +61325,7 @@
         <v>97</v>
       </c>
       <c r="D325" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="E325" t="s">
         <v>73</v>
@@ -61360,7 +61334,7 @@
         <v>67</v>
       </c>
       <c r="G325" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H325">
         <v>76000</v>
@@ -61525,7 +61499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="326" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>62</v>
       </c>
@@ -61536,7 +61510,7 @@
         <v>64</v>
       </c>
       <c r="D326" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E326" t="s">
         <v>73</v>
@@ -61545,7 +61519,7 @@
         <v>67</v>
       </c>
       <c r="G326" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H326">
         <v>155000</v>
@@ -61707,10 +61681,10 @@
         <v>1</v>
       </c>
       <c r="BJ326" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="327" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>62</v>
       </c>
@@ -61721,7 +61695,7 @@
         <v>64</v>
       </c>
       <c r="D327" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E327" t="s">
         <v>73</v>
@@ -61730,7 +61704,7 @@
         <v>67</v>
       </c>
       <c r="G327" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="H327">
         <v>100000</v>
@@ -61892,10 +61866,10 @@
         <v>0</v>
       </c>
       <c r="BJ327" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="328" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>62</v>
       </c>
@@ -61906,7 +61880,7 @@
         <v>97</v>
       </c>
       <c r="D328" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E328" t="s">
         <v>73</v>
@@ -61915,7 +61889,7 @@
         <v>67</v>
       </c>
       <c r="G328" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H328">
         <v>230000</v>
@@ -62077,13 +62051,13 @@
         <v>1</v>
       </c>
       <c r="BI328" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="BJ328" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="329" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>62</v>
       </c>
@@ -62094,7 +62068,7 @@
         <v>64</v>
       </c>
       <c r="D329" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="E329" t="s">
         <v>73</v>
@@ -62262,13 +62236,13 @@
         <v>0</v>
       </c>
       <c r="BI329" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="BJ329" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="330" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>62</v>
       </c>
@@ -62279,7 +62253,7 @@
         <v>97</v>
       </c>
       <c r="D330" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E330" t="s">
         <v>91</v>
@@ -62288,7 +62262,7 @@
         <v>67</v>
       </c>
       <c r="G330" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H330">
         <v>35000</v>
@@ -62450,13 +62424,13 @@
         <v>0</v>
       </c>
       <c r="BI330" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="BJ330" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="331" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>62</v>
       </c>
@@ -62467,7 +62441,7 @@
         <v>64</v>
       </c>
       <c r="D331" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E331" t="s">
         <v>73</v>
@@ -62476,7 +62450,7 @@
         <v>67</v>
       </c>
       <c r="G331" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H331">
         <v>60000</v>
@@ -62641,7 +62615,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="332" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>88</v>
       </c>
@@ -62652,7 +62626,7 @@
         <v>107</v>
       </c>
       <c r="D332" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E332" t="s">
         <v>91</v>
@@ -62661,7 +62635,7 @@
         <v>100</v>
       </c>
       <c r="G332" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H332">
         <v>40000</v>
@@ -62837,7 +62811,7 @@
         <v>97</v>
       </c>
       <c r="D333" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E333" t="s">
         <v>66</v>
@@ -63005,7 +62979,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="334" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -63016,7 +62990,7 @@
         <v>97</v>
       </c>
       <c r="D334" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E334" t="s">
         <v>73</v>
@@ -63025,7 +62999,7 @@
         <v>67</v>
       </c>
       <c r="G334" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H334">
         <v>39300</v>
@@ -63187,13 +63161,13 @@
         <v>0</v>
       </c>
       <c r="BI334" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="BJ334" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="335" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>88</v>
       </c>
@@ -63213,7 +63187,7 @@
         <v>67</v>
       </c>
       <c r="G335" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H335">
         <v>92000</v>
@@ -63375,7 +63349,7 @@
         <v>0</v>
       </c>
       <c r="BI335" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BJ335" t="s">
         <v>70</v>
@@ -63392,7 +63366,7 @@
         <v>97</v>
       </c>
       <c r="D336" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E336" t="s">
         <v>73</v>
@@ -63401,7 +63375,7 @@
         <v>67</v>
       </c>
       <c r="G336" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H336">
         <v>70000</v>
@@ -63566,7 +63540,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="337" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>88</v>
       </c>
@@ -63586,7 +63560,7 @@
         <v>67</v>
       </c>
       <c r="G337" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="H337">
         <v>45000</v>
@@ -63751,7 +63725,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="338" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>88</v>
       </c>
@@ -63762,7 +63736,7 @@
         <v>97</v>
       </c>
       <c r="D338" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E338" t="s">
         <v>73</v>
@@ -63771,7 +63745,7 @@
         <v>67</v>
       </c>
       <c r="G338" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I338">
         <v>0</v>
@@ -63930,13 +63904,13 @@
         <v>0</v>
       </c>
       <c r="BI338" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="BJ338" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="339" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>62</v>
       </c>
@@ -63947,7 +63921,7 @@
         <v>64</v>
       </c>
       <c r="D339" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E339" t="s">
         <v>73</v>
@@ -63956,7 +63930,7 @@
         <v>67</v>
       </c>
       <c r="G339" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H339">
         <v>64000</v>
@@ -64118,10 +64092,10 @@
         <v>1</v>
       </c>
       <c r="BJ339" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="340" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>62</v>
       </c>
@@ -64132,7 +64106,7 @@
         <v>64</v>
       </c>
       <c r="D340" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="E340" t="s">
         <v>73</v>
@@ -64141,7 +64115,7 @@
         <v>67</v>
       </c>
       <c r="G340" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H340">
         <v>40000</v>
@@ -64303,10 +64277,10 @@
         <v>0</v>
       </c>
       <c r="BJ340" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="341" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>88</v>
       </c>
@@ -64485,7 +64459,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="342" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>62</v>
       </c>
@@ -64496,7 +64470,7 @@
         <v>64</v>
       </c>
       <c r="D342" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E342" t="s">
         <v>66</v>
@@ -64664,7 +64638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="343" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>88</v>
       </c>
@@ -64675,7 +64649,7 @@
         <v>97</v>
       </c>
       <c r="D343" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E343" t="s">
         <v>73</v>
@@ -64684,7 +64658,7 @@
         <v>67</v>
       </c>
       <c r="G343" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="H343">
         <v>55000</v>
@@ -64849,7 +64823,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="344" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>88</v>
       </c>
@@ -64860,7 +64834,7 @@
         <v>97</v>
       </c>
       <c r="D344" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E344" t="s">
         <v>73</v>
@@ -64869,7 +64843,7 @@
         <v>67</v>
       </c>
       <c r="G344" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -65028,13 +65002,13 @@
         <v>0</v>
       </c>
       <c r="BI344" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="BJ344" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="345" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>62</v>
       </c>
@@ -65045,7 +65019,7 @@
         <v>64</v>
       </c>
       <c r="D345" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E345" t="s">
         <v>73</v>
@@ -65054,7 +65028,7 @@
         <v>67</v>
       </c>
       <c r="G345" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H345">
         <v>65000</v>
@@ -65216,13 +65190,13 @@
         <v>1</v>
       </c>
       <c r="BI345" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="BJ345" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="346" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>62</v>
       </c>
@@ -65242,7 +65216,7 @@
         <v>95</v>
       </c>
       <c r="G346" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H346">
         <v>40920</v>
@@ -65404,7 +65378,7 @@
         <v>0</v>
       </c>
       <c r="BI346" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="BJ346" t="s">
         <v>96</v>
@@ -65421,7 +65395,7 @@
         <v>97</v>
       </c>
       <c r="D347" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="E347" t="s">
         <v>73</v>
@@ -65430,7 +65404,7 @@
         <v>67</v>
       </c>
       <c r="G347" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H347">
         <v>200000</v>
@@ -65595,7 +65569,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="348" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>62</v>
       </c>
@@ -65615,7 +65589,7 @@
         <v>95</v>
       </c>
       <c r="G348" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H348">
         <v>40920</v>
@@ -65780,7 +65754,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="349" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>62</v>
       </c>
@@ -65800,7 +65774,7 @@
         <v>95</v>
       </c>
       <c r="G349" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H349">
         <v>40920</v>
@@ -65965,7 +65939,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="350" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>88</v>
       </c>
@@ -65985,7 +65959,7 @@
         <v>95</v>
       </c>
       <c r="G350" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="H350">
         <v>49000</v>
@@ -66147,13 +66121,13 @@
         <v>0</v>
       </c>
       <c r="BI350" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="BJ350" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="351" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>88</v>
       </c>
@@ -66164,7 +66138,7 @@
         <v>97</v>
       </c>
       <c r="D351" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E351" t="s">
         <v>73</v>
@@ -66329,10 +66303,10 @@
         <v>0</v>
       </c>
       <c r="BJ351" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="352" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>62</v>
       </c>
@@ -66343,7 +66317,7 @@
         <v>97</v>
       </c>
       <c r="D352" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E352" t="s">
         <v>66</v>
@@ -66352,7 +66326,7 @@
         <v>67</v>
       </c>
       <c r="G352" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H352">
         <v>75000</v>
@@ -66514,10 +66488,10 @@
         <v>0</v>
       </c>
       <c r="BI352" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="BJ352" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="353" spans="1:62" x14ac:dyDescent="0.3">
@@ -66531,7 +66505,7 @@
         <v>97</v>
       </c>
       <c r="D353" t="s">
-        <v>281</v>
+        <v>374</v>
       </c>
       <c r="E353" t="s">
         <v>73</v>
@@ -66540,7 +66514,7 @@
         <v>67</v>
       </c>
       <c r="G353" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="I353">
         <v>0</v>
@@ -66699,13 +66673,13 @@
         <v>0</v>
       </c>
       <c r="BI353" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="BJ353" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="354" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>62</v>
       </c>
@@ -66716,7 +66690,7 @@
         <v>97</v>
       </c>
       <c r="D354" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E354" t="s">
         <v>73</v>
@@ -66725,7 +66699,7 @@
         <v>67</v>
       </c>
       <c r="G354" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="H354">
         <v>42000</v>
@@ -66887,7 +66861,7 @@
         <v>0</v>
       </c>
       <c r="BJ354" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="355" spans="1:62" x14ac:dyDescent="0.3">
@@ -66901,7 +66875,7 @@
         <v>97</v>
       </c>
       <c r="D355" t="s">
-        <v>377</v>
+        <v>239</v>
       </c>
       <c r="E355" t="s">
         <v>73</v>
@@ -66910,7 +66884,7 @@
         <v>67</v>
       </c>
       <c r="G355" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="I355">
         <v>0</v>
@@ -67069,13 +67043,13 @@
         <v>0</v>
       </c>
       <c r="BI355" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="BJ355" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="356" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>88</v>
       </c>
@@ -67086,7 +67060,7 @@
         <v>107</v>
       </c>
       <c r="D356" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E356" t="s">
         <v>66</v>
@@ -67095,7 +67069,7 @@
         <v>67</v>
       </c>
       <c r="G356" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="H356">
         <v>70000</v>
@@ -67260,7 +67234,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="357" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>88</v>
       </c>
@@ -67271,7 +67245,7 @@
         <v>97</v>
       </c>
       <c r="D357" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="E357" t="s">
         <v>73</v>
@@ -67280,7 +67254,7 @@
         <v>67</v>
       </c>
       <c r="G357" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H357">
         <v>125000</v>
@@ -67442,13 +67416,13 @@
         <v>0</v>
       </c>
       <c r="BI357" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="BJ357" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="358" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>62</v>
       </c>
@@ -67468,7 +67442,7 @@
         <v>95</v>
       </c>
       <c r="G358" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="H358">
         <v>40920</v>
@@ -67630,13 +67604,13 @@
         <v>0</v>
       </c>
       <c r="BI358" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="BJ358" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="359" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>88</v>
       </c>
@@ -67647,7 +67621,7 @@
         <v>107</v>
       </c>
       <c r="D359" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E359" t="s">
         <v>94</v>
@@ -67656,7 +67630,7 @@
         <v>100</v>
       </c>
       <c r="G359" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H359">
         <v>58800</v>
@@ -67818,13 +67792,13 @@
         <v>1</v>
       </c>
       <c r="BI359" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="BJ359" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="360" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>88</v>
       </c>
@@ -67844,7 +67818,7 @@
         <v>100</v>
       </c>
       <c r="G360" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="H360">
         <v>48323</v>
@@ -68009,7 +67983,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="361" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>88</v>
       </c>
@@ -68029,7 +68003,7 @@
         <v>95</v>
       </c>
       <c r="G361" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H361">
         <v>48823</v>
@@ -68191,13 +68165,13 @@
         <v>1</v>
       </c>
       <c r="BI361" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="BJ361" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="362" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>88</v>
       </c>
@@ -68217,7 +68191,7 @@
         <v>95</v>
       </c>
       <c r="G362" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H362">
         <v>48823</v>
@@ -68382,7 +68356,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="363" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:62" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>88</v>
       </c>
@@ -68402,7 +68376,7 @@
         <v>95</v>
       </c>
       <c r="G363" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="H363">
         <v>40920</v>
@@ -68568,6 +68542,20 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BJ363" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="associate quality assurance engineer"/>
+        <filter val="executive quality assurance engineer"/>
+        <filter val="junior quality assurance engineer"/>
+        <filter val="quality assurance analyst"/>
+        <filter val="quality assurance engineer"/>
+        <filter val="quality assurance technologist"/>
+        <filter val="software qa engineer"/>
+        <filter val="software quality assurance engineer"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>